--- a/r4-core-main/StructureDefinition-at-core-organization.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-organization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3184" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3184" uniqueCount="433">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T09:19:25+00:00</t>
+    <t>2026-10-13T06:32:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1188,7 +1188,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-org-2:An address of an organization can never be of use 'home' {where(use = 'home').empty()}</t>
+org-2:An address of an organization can never be of use 'home' {where(use = 'home').empty()}at-addr-1:If the extension for street name is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-streetName').empty() or $this.hasValue())}at-addr-2:If the extension for street number is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-houseNumber').empty() or $this.hasValue())}at-addr-3:If the extension for floor/door number is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-additionalLocator').empty() or $this.hasValue())}</t>
   </si>
   <si>
     <t>ORC-23?</t>
@@ -1331,6 +1331,10 @@
   </si>
   <si>
     <t>May need to keep track of a contact party's address for contacting, billing or reporting requirements.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+at-addr-1:If the extension for street name is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-streetName').empty() or $this.hasValue())}at-addr-2:If the extension for street number is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-houseNumber').empty() or $this.hasValue())}at-addr-3:If the extension for floor/door number is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-additionalLocator').empty() or $this.hasValue())}</t>
   </si>
   <si>
     <t>PID-11</t>
@@ -11521,13 +11525,13 @@
         <v>21</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>99</v>
+        <v>425</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>21</v>
@@ -11538,10 +11542,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11564,17 +11568,17 @@
         <v>21</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>21</v>
@@ -11623,7 +11627,7 @@
         <v>21</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>

--- a/r4-core-main/StructureDefinition-at-core-organization.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T06:32:12+00:00</t>
+    <t>2026-10-13T12:58:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-organization.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T12:58:59+00:00</t>
+    <t>2026-10-19T05:20:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-organization.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T05:20:34+00:00</t>
+    <t>2026-10-19T13:05:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3589,10 +3589,10 @@
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S17" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="S17" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>201</v>
@@ -4611,10 +4611,10 @@
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S26" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="S26" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>21</v>
@@ -5301,10 +5301,10 @@
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S32" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="S32" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>201</v>
@@ -6323,10 +6323,10 @@
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S41" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="S41" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>21</v>
@@ -7013,10 +7013,10 @@
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S47" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="S47" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="T47" t="s" s="2">
         <v>201</v>
@@ -8035,10 +8035,10 @@
       </c>
       <c r="Q56" s="2"/>
       <c r="R56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S56" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="S56" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>21</v>
@@ -8725,10 +8725,10 @@
       </c>
       <c r="Q62" s="2"/>
       <c r="R62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S62" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="S62" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="T62" t="s" s="2">
         <v>201</v>
@@ -9747,10 +9747,10 @@
       </c>
       <c r="Q71" s="2"/>
       <c r="R71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S71" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="S71" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="T71" t="s" s="2">
         <v>21</v>

--- a/r4-core-main/StructureDefinition-at-core-organization.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-organization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3184" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3184" uniqueCount="441">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T13:05:38+00:00</t>
+    <t>2026-10-20T07:19:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -507,6 +507,12 @@
     <t>GDA-OID</t>
   </si>
   <si>
+    <t>Gesundheitsdiensteanbieter-OID (GDA-OID)</t>
+  </si>
+  <si>
+    <t>The OID of the healthcare service provider (Gesundheitsdiensteanbieter, GDA) as registered in the Austrian GDA-Index. The OID is assigned by the Federal Ministry of Health (Bundesministerium für Gesundheit).</t>
+  </si>
+  <si>
     <t>Organization.identifier:GDA-OID.id</t>
   </si>
   <si>
@@ -624,7 +630,7 @@
     <t>Organization.identifier.system</t>
   </si>
   <si>
-    <t>A GDA in Austria is represented via an URI (OID)</t>
+    <t>A Gesundheitsdiensteanbieter (GDA) in Austria is represented via a URI (OID)</t>
   </si>
   <si>
     <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
@@ -660,7 +666,7 @@
     <t>Organization.identifier.value</t>
   </si>
   <si>
-    <t>OID for the GDA in Austria</t>
+    <t>OID for the Gesundheitsdiensteanbieter (GDA) in Austria</t>
   </si>
   <si>
     <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
@@ -853,6 +859,12 @@
     <t>VPNR</t>
   </si>
   <si>
+    <t>Vertragspartnernummer (VPNR)</t>
+  </si>
+  <si>
+    <t>The contract partner number (Vertragspartnernummer, VPNR) of the organization, assigned by the Federation of Austrian Social Insurances (Dachverband der österreichischen Sozialversicherungsträger).</t>
+  </si>
+  <si>
     <t>Organization.identifier:VPNR.id</t>
   </si>
   <si>
@@ -913,6 +925,12 @@
     <t>VKZ</t>
   </si>
   <si>
+    <t>Verwaltungskennzeichen (VKZ)</t>
+  </si>
+  <si>
+    <t>The administrative identifier (Verwaltungskennzeichen, VKZ) of the organization, used in Austrian e-Government processes and assigned by the Federal Ministry of Finance (Bundesministerium für Finanzen).</t>
+  </si>
+  <si>
     <t>Organization.identifier:VKZ.id</t>
   </si>
   <si>
@@ -970,6 +988,12 @@
     <t>KANR</t>
   </si>
   <si>
+    <t>Krankenanstaltennummer (KA-Nr)</t>
+  </si>
+  <si>
+    <t>The hospital identification number (Krankenanstaltennummer, KA-Nr) of the organization according to the Austrian hospital register (Krankenanstaltenkataster), assigned by the Federal Ministry of Health (Österreichisches Bundesministerium für Gesundheit). Virtual KA-Nrs are suffixed with '+' (e.g. 'K101+').</t>
+  </si>
+  <si>
     <t>Organization.identifier:KANR.id</t>
   </si>
   <si>
@@ -994,7 +1018,7 @@
     <t>Organization.identifier:KANR.value</t>
   </si>
   <si>
-    <t>Krankenanstaltennummer according to Krankenanstaltenkataster. Virtual KANRs are suffixed with '+' (e.g. 'K101+')</t>
+    <t>Krankenanstaltennummer according to Krankenanstaltenkataster. Virtual KA-Nrs are suffixed with '+' (e.g. 'K101+')</t>
   </si>
   <si>
     <t>Organization.identifier:KANR.period</t>
@@ -3001,10 +3025,10 @@
         <v>145</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
@@ -3086,10 +3110,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3112,13 +3136,13 @@
         <v>21</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3169,7 +3193,7 @@
         <v>21</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3187,7 +3211,7 @@
         <v>21</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>21</v>
@@ -3198,10 +3222,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3230,7 +3254,7 @@
         <v>134</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="N14" t="s" s="2">
         <v>136</v>
@@ -3271,10 +3295,10 @@
         <v>21</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>21</v>
@@ -3283,7 +3307,7 @@
         <v>150</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3301,7 +3325,7 @@
         <v>21</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>21</v>
@@ -3312,10 +3336,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3341,16 +3365,16 @@
         <v>107</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>21</v>
@@ -3375,13 +3399,13 @@
         <v>21</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>21</v>
@@ -3399,7 +3423,7 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3417,7 +3441,7 @@
         <v>130</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>21</v>
@@ -3428,10 +3452,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3454,19 +3478,19 @@
         <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>21</v>
@@ -3491,13 +3515,13 @@
         <v>21</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>21</v>
@@ -3515,7 +3539,7 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3530,10 +3554,10 @@
         <v>99</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>21</v>
@@ -3544,10 +3568,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3573,16 +3597,16 @@
         <v>101</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>21</v>
@@ -3592,10 +3616,10 @@
         <v>21</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>21</v>
@@ -3631,7 +3655,7 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3646,13 +3670,13 @@
         <v>99</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>21</v>
@@ -3660,10 +3684,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3686,16 +3710,16 @@
         <v>88</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3709,7 +3733,7 @@
         <v>21</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="U18" t="s" s="2">
         <v>21</v>
@@ -3745,7 +3769,7 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3760,13 +3784,13 @@
         <v>99</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>21</v>
@@ -3774,10 +3798,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3800,13 +3824,13 @@
         <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3857,7 +3881,7 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3872,13 +3896,13 @@
         <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>21</v>
@@ -3886,10 +3910,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3912,16 +3936,16 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3971,7 +3995,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3986,13 +4010,13 @@
         <v>99</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>21</v>
@@ -4000,10 +4024,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4026,13 +4050,13 @@
         <v>21</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4083,7 +4107,7 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4101,7 +4125,7 @@
         <v>21</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>21</v>
@@ -4112,10 +4136,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4144,7 +4168,7 @@
         <v>134</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>136</v>
@@ -4185,10 +4209,10 @@
         <v>21</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>21</v>
@@ -4197,7 +4221,7 @@
         <v>150</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4215,7 +4239,7 @@
         <v>21</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>21</v>
@@ -4226,10 +4250,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4252,16 +4276,16 @@
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4311,7 +4335,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4320,7 +4344,7 @@
         <v>87</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>99</v>
@@ -4340,10 +4364,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4369,13 +4393,13 @@
         <v>101</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4401,13 +4425,13 @@
         <v>21</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>21</v>
@@ -4425,7 +4449,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4454,10 +4478,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4483,13 +4507,13 @@
         <v>145</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4539,7 +4563,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4557,7 +4581,7 @@
         <v>21</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>21</v>
@@ -4568,10 +4592,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4594,16 +4618,16 @@
         <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4614,7 +4638,7 @@
         <v>21</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>21</v>
@@ -4653,7 +4677,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4682,13 +4706,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>144</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>21</v>
@@ -4713,10 +4737,10 @@
         <v>145</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>146</v>
+        <v>272</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>147</v>
+        <v>273</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
@@ -4798,10 +4822,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4824,13 +4848,13 @@
         <v>21</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4881,7 +4905,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4899,7 +4923,7 @@
         <v>21</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>21</v>
@@ -4910,10 +4934,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4942,7 +4966,7 @@
         <v>134</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="N29" t="s" s="2">
         <v>136</v>
@@ -4983,10 +5007,10 @@
         <v>21</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>21</v>
@@ -4995,7 +5019,7 @@
         <v>150</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5013,7 +5037,7 @@
         <v>21</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>21</v>
@@ -5024,10 +5048,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5053,16 +5077,16 @@
         <v>107</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>21</v>
@@ -5087,13 +5111,13 @@
         <v>21</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>21</v>
@@ -5111,7 +5135,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5129,7 +5153,7 @@
         <v>130</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>21</v>
@@ -5140,10 +5164,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5166,19 +5190,19 @@
         <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>21</v>
@@ -5203,13 +5227,13 @@
         <v>21</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>21</v>
@@ -5227,7 +5251,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5242,10 +5266,10 @@
         <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>21</v>
@@ -5256,10 +5280,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5285,16 +5309,16 @@
         <v>101</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>21</v>
@@ -5304,10 +5328,10 @@
         <v>21</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="T32" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="U32" t="s" s="2">
         <v>21</v>
@@ -5343,7 +5367,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5358,13 +5382,13 @@
         <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>21</v>
@@ -5372,10 +5396,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5398,16 +5422,16 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5421,7 +5445,7 @@
         <v>21</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="U33" t="s" s="2">
         <v>21</v>
@@ -5457,7 +5481,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5472,13 +5496,13 @@
         <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>21</v>
@@ -5486,10 +5510,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5512,13 +5536,13 @@
         <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5569,7 +5593,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5584,13 +5608,13 @@
         <v>99</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>21</v>
@@ -5598,10 +5622,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5624,16 +5648,16 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5683,7 +5707,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5698,13 +5722,13 @@
         <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>21</v>
@@ -5712,10 +5736,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5738,13 +5762,13 @@
         <v>21</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5795,7 +5819,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5813,7 +5837,7 @@
         <v>21</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>21</v>
@@ -5824,10 +5848,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5856,7 +5880,7 @@
         <v>134</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="N37" t="s" s="2">
         <v>136</v>
@@ -5897,10 +5921,10 @@
         <v>21</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>21</v>
@@ -5909,7 +5933,7 @@
         <v>150</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5927,7 +5951,7 @@
         <v>21</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>21</v>
@@ -5938,10 +5962,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5964,16 +5988,16 @@
         <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6023,7 +6047,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6032,7 +6056,7 @@
         <v>87</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>99</v>
@@ -6052,10 +6076,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6081,13 +6105,13 @@
         <v>101</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6113,13 +6137,13 @@
         <v>21</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>21</v>
@@ -6137,7 +6161,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6166,10 +6190,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6195,13 +6219,13 @@
         <v>145</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6251,7 +6275,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6269,7 +6293,7 @@
         <v>21</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>21</v>
@@ -6280,10 +6304,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6306,16 +6330,16 @@
         <v>88</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6326,7 +6350,7 @@
         <v>21</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>21</v>
@@ -6365,7 +6389,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6394,13 +6418,13 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>144</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>21</v>
@@ -6425,10 +6449,10 @@
         <v>145</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>146</v>
+        <v>294</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>147</v>
+        <v>295</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
@@ -6510,10 +6534,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6536,13 +6560,13 @@
         <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6593,7 +6617,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6611,7 +6635,7 @@
         <v>21</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>21</v>
@@ -6622,10 +6646,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6654,7 +6678,7 @@
         <v>134</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>136</v>
@@ -6695,10 +6719,10 @@
         <v>21</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>21</v>
@@ -6707,7 +6731,7 @@
         <v>150</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6725,7 +6749,7 @@
         <v>21</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>21</v>
@@ -6736,10 +6760,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6765,16 +6789,16 @@
         <v>107</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>21</v>
@@ -6799,13 +6823,13 @@
         <v>21</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>21</v>
@@ -6823,7 +6847,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6841,7 +6865,7 @@
         <v>130</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>21</v>
@@ -6852,10 +6876,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6878,19 +6902,19 @@
         <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>21</v>
@@ -6915,13 +6939,13 @@
         <v>21</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>21</v>
@@ -6939,7 +6963,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6954,10 +6978,10 @@
         <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>21</v>
@@ -6968,10 +6992,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6997,16 +7021,16 @@
         <v>101</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>21</v>
@@ -7016,10 +7040,10 @@
         <v>21</v>
       </c>
       <c r="S47" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>21</v>
@@ -7055,7 +7079,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7070,13 +7094,13 @@
         <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>21</v>
@@ -7084,10 +7108,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7110,16 +7134,16 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7133,7 +7157,7 @@
         <v>21</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="U48" t="s" s="2">
         <v>21</v>
@@ -7169,7 +7193,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7184,13 +7208,13 @@
         <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>21</v>
@@ -7198,10 +7222,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7224,13 +7248,13 @@
         <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7281,7 +7305,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7296,13 +7320,13 @@
         <v>99</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>21</v>
@@ -7310,10 +7334,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7336,16 +7360,16 @@
         <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7395,7 +7419,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7410,13 +7434,13 @@
         <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>21</v>
@@ -7424,10 +7448,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7450,13 +7474,13 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7507,7 +7531,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7525,7 +7549,7 @@
         <v>21</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>21</v>
@@ -7536,10 +7560,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7568,7 +7592,7 @@
         <v>134</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>136</v>
@@ -7609,10 +7633,10 @@
         <v>21</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>21</v>
@@ -7621,7 +7645,7 @@
         <v>150</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7639,7 +7663,7 @@
         <v>21</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>21</v>
@@ -7650,10 +7674,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7676,16 +7700,16 @@
         <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7735,7 +7759,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7744,7 +7768,7 @@
         <v>87</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>99</v>
@@ -7764,10 +7788,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7793,13 +7817,13 @@
         <v>101</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7825,13 +7849,13 @@
         <v>21</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>21</v>
@@ -7849,7 +7873,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7878,10 +7902,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7907,13 +7931,13 @@
         <v>145</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7963,7 +7987,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7981,7 +8005,7 @@
         <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>21</v>
@@ -7992,10 +8016,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8018,16 +8042,16 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8038,7 +8062,7 @@
         <v>21</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>21</v>
@@ -8077,7 +8101,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8106,13 +8130,13 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>144</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="D57" t="s" s="2">
         <v>21</v>
@@ -8137,10 +8161,10 @@
         <v>145</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>146</v>
+        <v>315</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>147</v>
+        <v>316</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
@@ -8222,10 +8246,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8248,13 +8272,13 @@
         <v>21</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8305,7 +8329,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8323,7 +8347,7 @@
         <v>21</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>21</v>
@@ -8334,10 +8358,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8366,7 +8390,7 @@
         <v>134</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>136</v>
@@ -8407,10 +8431,10 @@
         <v>21</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>21</v>
@@ -8419,7 +8443,7 @@
         <v>150</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8437,7 +8461,7 @@
         <v>21</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>21</v>
@@ -8448,10 +8472,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8477,16 +8501,16 @@
         <v>107</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>21</v>
@@ -8511,13 +8535,13 @@
         <v>21</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>21</v>
@@ -8535,7 +8559,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8553,7 +8577,7 @@
         <v>130</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>21</v>
@@ -8564,10 +8588,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8590,19 +8614,19 @@
         <v>88</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>21</v>
@@ -8627,13 +8651,13 @@
         <v>21</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>21</v>
@@ -8651,7 +8675,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8666,10 +8690,10 @@
         <v>99</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>21</v>
@@ -8680,10 +8704,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8709,16 +8733,16 @@
         <v>101</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>21</v>
@@ -8728,10 +8752,10 @@
         <v>21</v>
       </c>
       <c r="S62" t="s" s="2">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="T62" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="U62" t="s" s="2">
         <v>21</v>
@@ -8767,7 +8791,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8782,13 +8806,13 @@
         <v>99</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>21</v>
@@ -8796,10 +8820,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8822,16 +8846,16 @@
         <v>88</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -8845,7 +8869,7 @@
         <v>21</v>
       </c>
       <c r="T63" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="U63" t="s" s="2">
         <v>21</v>
@@ -8881,7 +8905,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -8896,13 +8920,13 @@
         <v>99</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>21</v>
@@ -8910,10 +8934,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8936,13 +8960,13 @@
         <v>88</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8993,7 +9017,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9008,13 +9032,13 @@
         <v>99</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>21</v>
@@ -9022,10 +9046,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9048,16 +9072,16 @@
         <v>88</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9107,7 +9131,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9122,13 +9146,13 @@
         <v>99</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>21</v>
@@ -9136,10 +9160,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9162,13 +9186,13 @@
         <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9219,7 +9243,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9237,7 +9261,7 @@
         <v>21</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>21</v>
@@ -9248,10 +9272,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9280,7 +9304,7 @@
         <v>134</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>136</v>
@@ -9321,10 +9345,10 @@
         <v>21</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>21</v>
@@ -9333,7 +9357,7 @@
         <v>150</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9351,7 +9375,7 @@
         <v>21</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>21</v>
@@ -9362,10 +9386,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9388,16 +9412,16 @@
         <v>88</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9447,7 +9471,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9456,7 +9480,7 @@
         <v>87</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>99</v>
@@ -9476,10 +9500,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9505,13 +9529,13 @@
         <v>101</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9537,13 +9561,13 @@
         <v>21</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>21</v>
@@ -9561,7 +9585,7 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9590,10 +9614,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9619,13 +9643,13 @@
         <v>145</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9675,7 +9699,7 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -9693,7 +9717,7 @@
         <v>21</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>21</v>
@@ -9704,10 +9728,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9730,16 +9754,16 @@
         <v>88</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -9750,7 +9774,7 @@
         <v>21</v>
       </c>
       <c r="S71" t="s" s="2">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="T71" t="s" s="2">
         <v>21</v>
@@ -9789,7 +9813,7 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -9818,10 +9842,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9844,25 +9868,25 @@
         <v>88</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q72" t="s" s="2">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="R72" t="s" s="2">
         <v>21</v>
@@ -9907,7 +9931,7 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -9922,24 +9946,24 @@
         <v>99</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>337</v>
+        <v>345</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9962,19 +9986,19 @@
         <v>88</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>21</v>
@@ -9999,11 +10023,11 @@
         <v>21</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>21</v>
@@ -10021,7 +10045,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10036,24 +10060,24 @@
         <v>99</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>346</v>
+        <v>354</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10076,19 +10100,19 @@
         <v>88</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>21</v>
@@ -10137,7 +10161,7 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10152,13 +10176,13 @@
         <v>99</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>21</v>
@@ -10166,10 +10190,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10192,19 +10216,19 @@
         <v>21</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>21</v>
@@ -10253,7 +10277,7 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10271,7 +10295,7 @@
         <v>21</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>21</v>
@@ -10282,10 +10306,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10308,19 +10332,19 @@
         <v>21</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>21</v>
@@ -10369,7 +10393,7 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -10378,19 +10402,19 @@
         <v>79</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>21</v>
@@ -10398,10 +10422,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10424,19 +10448,19 @@
         <v>21</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>21</v>
@@ -10485,7 +10509,7 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -10494,19 +10518,19 @@
         <v>79</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>21</v>
@@ -10514,10 +10538,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10540,17 +10564,17 @@
         <v>88</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>21</v>
@@ -10599,7 +10623,7 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -10614,13 +10638,13 @@
         <v>99</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>21</v>
@@ -10628,10 +10652,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10654,19 +10678,19 @@
         <v>21</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>21</v>
@@ -10715,7 +10739,7 @@
         <v>21</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -10733,7 +10757,7 @@
         <v>21</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>21</v>
@@ -10744,10 +10768,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10770,13 +10794,13 @@
         <v>21</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -10827,7 +10851,7 @@
         <v>21</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -10845,7 +10869,7 @@
         <v>21</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>21</v>
@@ -10856,10 +10880,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10888,7 +10912,7 @@
         <v>134</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>136</v>
@@ -10941,7 +10965,7 @@
         <v>21</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -10959,7 +10983,7 @@
         <v>21</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>21</v>
@@ -10970,14 +10994,14 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -10999,10 +11023,10 @@
         <v>133</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="N82" t="s" s="2">
         <v>136</v>
@@ -11057,7 +11081,7 @@
         <v>21</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -11086,10 +11110,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11112,17 +11136,17 @@
         <v>21</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>21</v>
@@ -11147,13 +11171,13 @@
         <v>21</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>21</v>
@@ -11171,7 +11195,7 @@
         <v>21</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -11189,7 +11213,7 @@
         <v>21</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>21</v>
@@ -11200,10 +11224,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11226,17 +11250,17 @@
         <v>21</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>21</v>
@@ -11285,7 +11309,7 @@
         <v>21</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -11300,10 +11324,10 @@
         <v>99</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>21</v>
@@ -11314,10 +11338,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11340,17 +11364,17 @@
         <v>21</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" t="s" s="2">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>21</v>
@@ -11399,7 +11423,7 @@
         <v>21</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -11414,10 +11438,10 @@
         <v>99</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>21</v>
@@ -11428,10 +11452,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11454,17 +11478,17 @@
         <v>21</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>21</v>
@@ -11513,7 +11537,7 @@
         <v>21</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -11525,13 +11549,13 @@
         <v>21</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>21</v>
@@ -11542,10 +11566,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11568,17 +11592,17 @@
         <v>21</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" t="s" s="2">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>21</v>
@@ -11627,7 +11651,7 @@
         <v>21</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -11645,7 +11669,7 @@
         <v>21</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>21</v>
